--- a/15min.xlsx
+++ b/15min.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2770" uniqueCount="2770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="2690">
   <si>
     <t xml:space="preserve">PERIOD 
 DD.MM.YYYY HH:MM</t>
@@ -19,246 +19,6 @@
   <si>
     <t xml:space="preserve">VALUE
 (use D for delete)</t>
-  </si>
-  <si>
-    <t>31.01.2026 04:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 04:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 04:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 04:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 05:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 05:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 05:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 05:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 06:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 06:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 06:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 06:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 07:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 07:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 07:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 07:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 08:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 08:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 08:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 08:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 09:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 09:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 09:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 09:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 10:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 10:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 10:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 10:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 11:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 11:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 11:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 11:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 12:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 12:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 12:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 12:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 13:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 13:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 13:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 13:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 14:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 14:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 14:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 14:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 15:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 15:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 15:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 15:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 16:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 16:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 16:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 16:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 17:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 17:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 17:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 17:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 18:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 18:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 18:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 18:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 19:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 19:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 19:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 19:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 20:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 20:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 20:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 20:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 21:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 21:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 21:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 21:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 22:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 22:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 22:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 22:45</t>
-  </si>
-  <si>
-    <t>31.01.2026 23:00</t>
-  </si>
-  <si>
-    <t>31.01.2026 23:15</t>
-  </si>
-  <si>
-    <t>31.01.2026 23:30</t>
-  </si>
-  <si>
-    <t>31.01.2026 23:45</t>
   </si>
   <si>
     <t>01.02.2026 00:00</t>
@@ -8704,7 +8464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2769"/>
+  <dimension ref="A1:B2689"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -30219,646 +29979,6 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2690" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2690" t="s">
-        <v>2690</v>
-      </c>
-      <c r="B2690">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2691" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2691" t="s">
-        <v>2691</v>
-      </c>
-      <c r="B2691">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2692" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2692" t="s">
-        <v>2692</v>
-      </c>
-      <c r="B2692">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2693" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2693" t="s">
-        <v>2693</v>
-      </c>
-      <c r="B2693">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2694" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2694" t="s">
-        <v>2694</v>
-      </c>
-      <c r="B2694">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2695" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2695" t="s">
-        <v>2695</v>
-      </c>
-      <c r="B2695">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2696" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2696" t="s">
-        <v>2696</v>
-      </c>
-      <c r="B2696">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2697" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2697" t="s">
-        <v>2697</v>
-      </c>
-      <c r="B2697">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2698" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2698" t="s">
-        <v>2698</v>
-      </c>
-      <c r="B2698">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2699" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2699" t="s">
-        <v>2699</v>
-      </c>
-      <c r="B2699">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2700" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2700" t="s">
-        <v>2700</v>
-      </c>
-      <c r="B2700">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2701" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2701" t="s">
-        <v>2701</v>
-      </c>
-      <c r="B2701">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2702" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2702" t="s">
-        <v>2702</v>
-      </c>
-      <c r="B2702">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2703" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2703" t="s">
-        <v>2703</v>
-      </c>
-      <c r="B2703">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2704" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2704" t="s">
-        <v>2704</v>
-      </c>
-      <c r="B2704">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2705" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2705" t="s">
-        <v>2705</v>
-      </c>
-      <c r="B2705">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2706" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2706" t="s">
-        <v>2706</v>
-      </c>
-      <c r="B2706">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2707" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2707" t="s">
-        <v>2707</v>
-      </c>
-      <c r="B2707">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2708" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2708" t="s">
-        <v>2708</v>
-      </c>
-      <c r="B2708">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2709" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2709" t="s">
-        <v>2709</v>
-      </c>
-      <c r="B2709">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2710" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2710" t="s">
-        <v>2710</v>
-      </c>
-      <c r="B2710">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2711" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2711" t="s">
-        <v>2711</v>
-      </c>
-      <c r="B2711">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2712" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2712" t="s">
-        <v>2712</v>
-      </c>
-      <c r="B2712">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2713" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2713" t="s">
-        <v>2713</v>
-      </c>
-      <c r="B2713">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2714" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2714" t="s">
-        <v>2714</v>
-      </c>
-      <c r="B2714">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2715" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2715" t="s">
-        <v>2715</v>
-      </c>
-      <c r="B2715">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2716" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2716" t="s">
-        <v>2716</v>
-      </c>
-      <c r="B2716">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2717" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2717" t="s">
-        <v>2717</v>
-      </c>
-      <c r="B2717">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2718" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2718" t="s">
-        <v>2718</v>
-      </c>
-      <c r="B2718">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2719" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2719" t="s">
-        <v>2719</v>
-      </c>
-      <c r="B2719">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2720" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2720" t="s">
-        <v>2720</v>
-      </c>
-      <c r="B2720">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2721" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2721" t="s">
-        <v>2721</v>
-      </c>
-      <c r="B2721">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2722" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2722" t="s">
-        <v>2722</v>
-      </c>
-      <c r="B2722">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2723" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2723" t="s">
-        <v>2723</v>
-      </c>
-      <c r="B2723">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2724" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2724" t="s">
-        <v>2724</v>
-      </c>
-      <c r="B2724">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2725" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2725" t="s">
-        <v>2725</v>
-      </c>
-      <c r="B2725">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2726" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2726" t="s">
-        <v>2726</v>
-      </c>
-      <c r="B2726">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2727" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2727" t="s">
-        <v>2727</v>
-      </c>
-      <c r="B2727">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2728" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2728" t="s">
-        <v>2728</v>
-      </c>
-      <c r="B2728">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2729" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2729" t="s">
-        <v>2729</v>
-      </c>
-      <c r="B2729">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2730" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2730" t="s">
-        <v>2730</v>
-      </c>
-      <c r="B2730">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2731" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2731" t="s">
-        <v>2731</v>
-      </c>
-      <c r="B2731">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2732" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2732" t="s">
-        <v>2732</v>
-      </c>
-      <c r="B2732">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2733" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2733" t="s">
-        <v>2733</v>
-      </c>
-      <c r="B2733">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2734" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2734" t="s">
-        <v>2734</v>
-      </c>
-      <c r="B2734">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2735" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2735" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B2735">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2736" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2736" t="s">
-        <v>2736</v>
-      </c>
-      <c r="B2736">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2737" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2737" t="s">
-        <v>2737</v>
-      </c>
-      <c r="B2737">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2738" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2738" t="s">
-        <v>2738</v>
-      </c>
-      <c r="B2738">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2739" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2739" t="s">
-        <v>2739</v>
-      </c>
-      <c r="B2739">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2740" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2740" t="s">
-        <v>2740</v>
-      </c>
-      <c r="B2740">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2741" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2741" t="s">
-        <v>2741</v>
-      </c>
-      <c r="B2741">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2742" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2742" t="s">
-        <v>2742</v>
-      </c>
-      <c r="B2742">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2743" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2743" t="s">
-        <v>2743</v>
-      </c>
-      <c r="B2743">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2744" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2744" t="s">
-        <v>2744</v>
-      </c>
-      <c r="B2744">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2745" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2745" t="s">
-        <v>2745</v>
-      </c>
-      <c r="B2745">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2746" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2746" t="s">
-        <v>2746</v>
-      </c>
-      <c r="B2746">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2747" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2747" t="s">
-        <v>2747</v>
-      </c>
-      <c r="B2747">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2748" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2748" t="s">
-        <v>2748</v>
-      </c>
-      <c r="B2748">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2749" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2749" t="s">
-        <v>2749</v>
-      </c>
-      <c r="B2749">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2750" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2750" t="s">
-        <v>2750</v>
-      </c>
-      <c r="B2750">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2751" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2751" t="s">
-        <v>2751</v>
-      </c>
-      <c r="B2751">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2752" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2752" t="s">
-        <v>2752</v>
-      </c>
-      <c r="B2752">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2753" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2753" t="s">
-        <v>2753</v>
-      </c>
-      <c r="B2753">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2754" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2754" t="s">
-        <v>2754</v>
-      </c>
-      <c r="B2754">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2755" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2755" t="s">
-        <v>2755</v>
-      </c>
-      <c r="B2755">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2756" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2756" t="s">
-        <v>2756</v>
-      </c>
-      <c r="B2756">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2757" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2757" t="s">
-        <v>2757</v>
-      </c>
-      <c r="B2757">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2758" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2758" t="s">
-        <v>2758</v>
-      </c>
-      <c r="B2758">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2759" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2759" t="s">
-        <v>2759</v>
-      </c>
-      <c r="B2759">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2760" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2760" t="s">
-        <v>2760</v>
-      </c>
-      <c r="B2760">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2761" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2761" t="s">
-        <v>2761</v>
-      </c>
-      <c r="B2761">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2762" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2762" t="s">
-        <v>2762</v>
-      </c>
-      <c r="B2762">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2763" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2763" t="s">
-        <v>2763</v>
-      </c>
-      <c r="B2763">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2764" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2764" t="s">
-        <v>2764</v>
-      </c>
-      <c r="B2764">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2765" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2765" t="s">
-        <v>2765</v>
-      </c>
-      <c r="B2765">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2766" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2766" t="s">
-        <v>2766</v>
-      </c>
-      <c r="B2766">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2767" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2767" t="s">
-        <v>2767</v>
-      </c>
-      <c r="B2767">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2768" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2768" t="s">
-        <v>2768</v>
-      </c>
-      <c r="B2768">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2769" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2769" t="s">
-        <v>2769</v>
-      </c>
-      <c r="B2769">
-        <v>100</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
